--- a/output_phyto/phyto_Intermediate_zhang_2019.xlsx
+++ b/output_phyto/phyto_Intermediate_zhang_2019.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="382">
   <si>
     <t>NA</t>
   </si>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_1</t>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_1</t>
   </si>
   <si>
     <t xml:space="preserve">10.1016/j.gca.2019.06.032</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_zhang_2019.xlsx</t>
+    <t xml:space="preserve">phytoplankton_zhang_2019_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
-    <t xml:space="preserve">alkenone unsaturation</t>
+    <t xml:space="preserve">published Uk37 temperature</t>
   </si>
   <si>
     <t xml:space="preserve">Zhang et al., 2013</t>
@@ -1484,79 +1484,103 @@
     <t xml:space="preserve">The calculation of d13C_CO2aq is not described, but assume it follows Zhang et al. (2013)</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_2</t>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_2</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_2</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_3</t>
+    <t xml:space="preserve">phytoplankton_zhang_2020_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_3</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_3</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_4</t>
+    <t xml:space="preserve">phytoplankton_zhang_2020_23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_4</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_4</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_5</t>
+    <t xml:space="preserve">phytoplankton_zhang_2020_24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_5</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_5</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_6</t>
+    <t xml:space="preserve">phytoplankton_zhang_2020_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_6</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_6</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_7</t>
+    <t xml:space="preserve">phytoplankton_zhang_2020_26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_7</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_7</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_8</t>
+    <t xml:space="preserve">phytoplankton_zhang_2020_27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_8</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_8</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_9</t>
+    <t xml:space="preserve">phytoplankton_zhang_2020_28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_9</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_9</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_10</t>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_10</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_10</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_11</t>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_11</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_11</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_12</t>
+    <t xml:space="preserve">phytoplankton_zhang_2020_29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_12</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_12</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_13</t>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_13</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_13</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_14</t>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_14</t>
   </si>
   <si>
     <t xml:space="preserve">Dong et al., 2016. Tuned high-resolution Tex86 record to EPICA Dome C CO2 record.</t>
@@ -1565,277 +1589,205 @@
     <t xml:space="preserve">Locarnini et al., 2010</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">The calculation of d13C_CO2aq is not described, but assume it follows Zhang et al. (2013). Subtracted 0.5‰ from the d13C_CaCO3 value reported in the supplementary table of Zhang et al. (2019) to get back to actual measured foraminifera d13C, since the reported value in the table includes the vital effect.</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_37</t>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_37</t>
   </si>
   <si>
     <t xml:space="preserve">Tuned G. ruber d18O record to LR04 stack (Bird and Cali, 2002; Hönisch et al., 2009).</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Williams and Kohl (1986); Imbrie et al. (1984).; Jasper and Gagosian (1989) details the age model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2019_80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Jasper_1990_28</t>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_58</t>
   </si>
 </sst>
 </file>
@@ -1843,7 +1795,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1909,12 +1861,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -2028,7 +1974,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2127,7 +2073,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2853,7 +2798,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2871,8 +2816,8 @@
       <c r="H5" t="n">
         <v>0.01659048</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2890,7 +2835,7 @@
         <v>-23.871</v>
       </c>
       <c r="O5" t="n">
-        <v>0.074</v>
+        <v>0.0523259018078045</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2901,8 +2846,8 @@
       <c r="R5" s="11" t="n">
         <v>27.36093</v>
       </c>
-      <c r="S5" t="e">
-        <v>#N/A</v>
+      <c r="S5" t="n">
+        <v>3</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2919,29 +2864,29 @@
       <c r="X5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z5" t="e">
-        <v>#N/A</v>
+      <c r="Y5" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA5" t="s">
         <v>277</v>
       </c>
-      <c r="AB5" t="e">
-        <v>#N/A</v>
+      <c r="AB5" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF5" t="e">
-        <v>#N/A</v>
+      <c r="AD5" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG5" t="e">
         <v>#N/A</v>
@@ -2963,7 +2908,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2981,8 +2926,8 @@
       <c r="H6" t="n">
         <v>0.02999447</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.004</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -3000,7 +2945,7 @@
         <v>-23.543</v>
       </c>
       <c r="O6" t="n">
-        <v>0.118</v>
+        <v>0.0834386001800126</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -3011,8 +2956,8 @@
       <c r="R6" s="11" t="n">
         <v>27.08687</v>
       </c>
-      <c r="S6" t="e">
-        <v>#N/A</v>
+      <c r="S6" t="n">
+        <v>3</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -3029,29 +2974,29 @@
       <c r="X6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z6" t="e">
-        <v>#N/A</v>
+      <c r="Y6" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA6" t="s">
         <v>277</v>
       </c>
-      <c r="AB6" t="e">
-        <v>#N/A</v>
+      <c r="AB6" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" t="e">
-        <v>#N/A</v>
+      <c r="AD6" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG6" t="e">
         <v>#N/A</v>
@@ -3059,8 +3004,8 @@
       <c r="AH6" t="s">
         <v>281</v>
       </c>
-      <c r="AI6" t="e">
-        <v>#N/A</v>
+      <c r="AI6" t="s">
+        <v>282</v>
       </c>
       <c r="AJ6" t="s">
         <v>279</v>
@@ -3068,12 +3013,12 @@
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -3091,8 +3036,8 @@
       <c r="H7" t="n">
         <v>0.03954827</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.004</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -3110,7 +3055,7 @@
         <v>-24.05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.414</v>
+        <v>0.292742207411231</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -3121,8 +3066,8 @@
       <c r="R7" s="11" t="n">
         <v>27.29793</v>
       </c>
-      <c r="S7" t="e">
-        <v>#N/A</v>
+      <c r="S7" t="n">
+        <v>3</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -3139,38 +3084,38 @@
       <c r="X7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z7" t="e">
-        <v>#N/A</v>
+      <c r="Y7" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA7" t="s">
         <v>277</v>
       </c>
-      <c r="AB7" t="e">
-        <v>#N/A</v>
+      <c r="AB7" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF7" t="e">
-        <v>#N/A</v>
+      <c r="AD7" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG7" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH7" t="s">
-        <v>283</v>
-      </c>
-      <c r="AI7" t="e">
-        <v>#N/A</v>
+        <v>284</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>285</v>
       </c>
       <c r="AJ7" t="s">
         <v>279</v>
@@ -3178,12 +3123,12 @@
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -3201,8 +3146,8 @@
       <c r="H8" t="n">
         <v>0.04910211</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.004</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -3220,7 +3165,7 @@
         <v>-23.8055</v>
       </c>
       <c r="O8" t="n">
-        <v>0.15</v>
+        <v>0.106066017177982</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -3231,8 +3176,8 @@
       <c r="R8" s="11" t="n">
         <v>26.51978</v>
       </c>
-      <c r="S8" t="e">
-        <v>#N/A</v>
+      <c r="S8" t="n">
+        <v>3</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -3249,38 +3194,38 @@
       <c r="X8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z8" t="e">
-        <v>#N/A</v>
+      <c r="Y8" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA8" t="s">
         <v>277</v>
       </c>
-      <c r="AB8" t="e">
-        <v>#N/A</v>
+      <c r="AB8" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF8" t="e">
-        <v>#N/A</v>
+      <c r="AD8" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG8" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH8" t="s">
-        <v>285</v>
-      </c>
-      <c r="AI8" t="e">
-        <v>#N/A</v>
+        <v>287</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>288</v>
       </c>
       <c r="AJ8" t="s">
         <v>279</v>
@@ -3288,12 +3233,12 @@
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3311,8 +3256,8 @@
       <c r="H9" t="n">
         <v>0.06147872</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3330,7 +3275,7 @@
         <v>-23.969</v>
       </c>
       <c r="O9" t="n">
-        <v>0.488</v>
+        <v>0.345068109219035</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3341,8 +3286,8 @@
       <c r="R9" s="11" t="n">
         <v>27.01086</v>
       </c>
-      <c r="S9" t="e">
-        <v>#N/A</v>
+      <c r="S9" t="n">
+        <v>3</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3359,38 +3304,38 @@
       <c r="X9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z9" t="e">
-        <v>#N/A</v>
+      <c r="Y9" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA9" t="s">
         <v>277</v>
       </c>
-      <c r="AB9" t="e">
-        <v>#N/A</v>
+      <c r="AB9" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" t="e">
-        <v>#N/A</v>
+      <c r="AD9" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG9" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH9" t="s">
-        <v>287</v>
-      </c>
-      <c r="AI9" t="e">
-        <v>#N/A</v>
+        <v>290</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>291</v>
       </c>
       <c r="AJ9" t="s">
         <v>279</v>
@@ -3398,12 +3343,12 @@
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3421,8 +3366,8 @@
       <c r="H10" t="n">
         <v>0.0746889</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.004</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3440,7 +3385,7 @@
         <v>-24.34</v>
       </c>
       <c r="O10" t="n">
-        <v>0.224</v>
+        <v>0.158391918985787</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3451,8 +3396,8 @@
       <c r="R10" s="11" t="n">
         <v>27.57143</v>
       </c>
-      <c r="S10" t="e">
-        <v>#N/A</v>
+      <c r="S10" t="n">
+        <v>3</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3469,38 +3414,38 @@
       <c r="X10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z10" t="e">
-        <v>#N/A</v>
+      <c r="Y10" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA10" t="s">
         <v>277</v>
       </c>
-      <c r="AB10" t="e">
-        <v>#N/A</v>
+      <c r="AB10" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF10" t="e">
-        <v>#N/A</v>
+      <c r="AD10" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG10" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH10" t="s">
-        <v>289</v>
-      </c>
-      <c r="AI10" t="e">
-        <v>#N/A</v>
+        <v>293</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>294</v>
       </c>
       <c r="AJ10" t="s">
         <v>279</v>
@@ -3508,12 +3453,12 @@
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3531,8 +3476,8 @@
       <c r="H11" t="n">
         <v>0.08938702</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.004</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3550,7 +3495,7 @@
         <v>-24.2365</v>
       </c>
       <c r="O11" t="n">
-        <v>0.406</v>
+        <v>0.287085353161738</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3561,8 +3506,8 @@
       <c r="R11" s="11" t="n">
         <v>27.63915</v>
       </c>
-      <c r="S11" t="e">
-        <v>#N/A</v>
+      <c r="S11" t="n">
+        <v>3</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3579,38 +3524,38 @@
       <c r="X11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z11" t="e">
-        <v>#N/A</v>
+      <c r="Y11" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA11" t="s">
         <v>277</v>
       </c>
-      <c r="AB11" t="e">
-        <v>#N/A</v>
+      <c r="AB11" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF11" t="e">
-        <v>#N/A</v>
+      <c r="AD11" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG11" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH11" t="s">
-        <v>291</v>
-      </c>
-      <c r="AI11" t="e">
-        <v>#N/A</v>
+        <v>296</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>297</v>
       </c>
       <c r="AJ11" t="s">
         <v>279</v>
@@ -3618,12 +3563,12 @@
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3641,8 +3586,8 @@
       <c r="H12" t="n">
         <v>0.1013744</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.004</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3660,7 +3605,7 @@
         <v>-23.994</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1</v>
+        <v>0.0707106781186548</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3671,8 +3616,8 @@
       <c r="R12" s="11" t="n">
         <v>27.72457</v>
       </c>
-      <c r="S12" t="e">
-        <v>#N/A</v>
+      <c r="S12" t="n">
+        <v>3</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3689,38 +3634,38 @@
       <c r="X12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z12" t="e">
-        <v>#N/A</v>
+      <c r="Y12" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA12" t="s">
         <v>277</v>
       </c>
-      <c r="AB12" t="e">
-        <v>#N/A</v>
+      <c r="AB12" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" t="e">
-        <v>#N/A</v>
+      <c r="AD12" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG12" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH12" t="s">
-        <v>293</v>
-      </c>
-      <c r="AI12" t="e">
-        <v>#N/A</v>
+        <v>299</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>300</v>
       </c>
       <c r="AJ12" t="s">
         <v>279</v>
@@ -3728,12 +3673,12 @@
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3751,8 +3696,8 @@
       <c r="H13" t="n">
         <v>0.1158935</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.004</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3770,7 +3715,7 @@
         <v>-24.3845</v>
       </c>
       <c r="O13" t="n">
-        <v>0.168</v>
+        <v>0.11879393923934</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3781,8 +3726,8 @@
       <c r="R13" s="11" t="n">
         <v>27.7677</v>
       </c>
-      <c r="S13" t="e">
-        <v>#N/A</v>
+      <c r="S13" t="n">
+        <v>3</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3799,35 +3744,35 @@
       <c r="X13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z13" t="e">
-        <v>#N/A</v>
+      <c r="Y13" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA13" t="s">
         <v>277</v>
       </c>
-      <c r="AB13" t="e">
-        <v>#N/A</v>
+      <c r="AB13" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF13" t="e">
-        <v>#N/A</v>
+      <c r="AD13" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG13" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH13" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AI13" t="e">
         <v>#N/A</v>
@@ -3838,12 +3783,12 @@
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3861,8 +3806,8 @@
       <c r="H14" t="n">
         <v>0.132497</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.004</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3880,7 +3825,7 @@
         <v>-24.6465</v>
       </c>
       <c r="O14" t="n">
-        <v>0.066</v>
+        <v>0.0466690475583121</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3891,8 +3836,8 @@
       <c r="R14" s="11" t="n">
         <v>27.84511</v>
       </c>
-      <c r="S14" t="e">
-        <v>#N/A</v>
+      <c r="S14" t="n">
+        <v>3</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3909,35 +3854,35 @@
       <c r="X14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z14" t="e">
-        <v>#N/A</v>
+      <c r="Y14" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA14" t="s">
         <v>277</v>
       </c>
-      <c r="AB14" t="e">
-        <v>#N/A</v>
+      <c r="AB14" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" t="e">
-        <v>#N/A</v>
+      <c r="AD14" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH14" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="AI14" t="e">
         <v>#N/A</v>
@@ -3948,12 +3893,12 @@
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3971,8 +3916,8 @@
       <c r="H15" t="n">
         <v>0.1432684</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.004</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3990,7 +3935,7 @@
         <v>-24.3855</v>
       </c>
       <c r="O15" t="n">
-        <v>0.324</v>
+        <v>0.229102597104441</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -4001,8 +3946,8 @@
       <c r="R15" s="11" t="n">
         <v>27.58889</v>
       </c>
-      <c r="S15" t="e">
-        <v>#N/A</v>
+      <c r="S15" t="n">
+        <v>3</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -4019,38 +3964,38 @@
       <c r="X15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z15" t="e">
-        <v>#N/A</v>
+      <c r="Y15" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA15" t="s">
         <v>277</v>
       </c>
-      <c r="AB15" t="e">
-        <v>#N/A</v>
+      <c r="AB15" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" t="e">
-        <v>#N/A</v>
+      <c r="AD15" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG15" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH15" t="s">
-        <v>299</v>
-      </c>
-      <c r="AI15" t="e">
-        <v>#N/A</v>
+        <v>306</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>307</v>
       </c>
       <c r="AJ15" t="s">
         <v>279</v>
@@ -4058,12 +4003,12 @@
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -4081,8 +4026,8 @@
       <c r="H16" t="n">
         <v>0.15369086</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.004</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -4100,7 +4045,7 @@
         <v>-24.1665</v>
       </c>
       <c r="O16" t="n">
-        <v>0.298</v>
+        <v>0.210717820793591</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -4111,8 +4056,8 @@
       <c r="R16" s="11" t="n">
         <v>27.22344</v>
       </c>
-      <c r="S16" t="e">
-        <v>#N/A</v>
+      <c r="S16" t="n">
+        <v>3</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -4129,35 +4074,35 @@
       <c r="X16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z16" t="e">
-        <v>#N/A</v>
+      <c r="Y16" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA16" t="s">
         <v>277</v>
       </c>
-      <c r="AB16" t="e">
-        <v>#N/A</v>
+      <c r="AB16" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF16" t="e">
-        <v>#N/A</v>
+      <c r="AD16" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG16" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH16" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="AI16" t="e">
         <v>#N/A</v>
@@ -4168,12 +4113,12 @@
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -4191,8 +4136,8 @@
       <c r="H17" t="n">
         <v>0.16553608</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.004</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -4210,7 +4155,7 @@
         <v>-24.5575</v>
       </c>
       <c r="O17" t="n">
-        <v>0.396</v>
+        <v>0.280014285349873</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -4221,8 +4166,8 @@
       <c r="R17" s="11" t="n">
         <v>27.08438</v>
       </c>
-      <c r="S17" t="e">
-        <v>#N/A</v>
+      <c r="S17" t="n">
+        <v>3</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -4239,35 +4184,35 @@
       <c r="X17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z17" t="e">
-        <v>#N/A</v>
+      <c r="Y17" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA17" t="s">
         <v>277</v>
       </c>
-      <c r="AB17" t="e">
-        <v>#N/A</v>
+      <c r="AB17" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF17" t="e">
-        <v>#N/A</v>
+      <c r="AD17" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG17" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH17" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="AI17" t="e">
         <v>#N/A</v>
@@ -4278,12 +4223,12 @@
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4301,8 +4246,8 @@
       <c r="H18" t="n">
         <v>0.03712489</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.004</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4311,7 +4256,7 @@
         <v>#N/A</v>
       </c>
       <c r="L18" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M18" t="s">
         <v>275</v>
@@ -4320,7 +4265,7 @@
         <v>-24.44</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04</v>
+        <v>0.0282842712474619</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4332,7 +4277,7 @@
         <v>24.6336722027576</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4257639177681</v>
+        <v>3</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -4349,29 +4294,29 @@
       <c r="X18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z18" t="e">
-        <v>#N/A</v>
+      <c r="Y18" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA18" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB18" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" t="e">
-        <v>#N/A</v>
+      <c r="AD18" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG18" t="e">
         <v>#N/A</v>
@@ -4379,21 +4324,21 @@
       <c r="AH18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI18" t="e">
-        <v>#N/A</v>
+      <c r="AI18" t="s">
+        <v>315</v>
       </c>
       <c r="AJ18" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4411,8 +4356,8 @@
       <c r="H19" t="n">
         <v>0.037591</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.004</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4421,7 +4366,7 @@
         <v>#N/A</v>
       </c>
       <c r="L19" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M19" t="s">
         <v>275</v>
@@ -4430,7 +4375,7 @@
         <v>-24.69</v>
       </c>
       <c r="O19" t="n">
-        <v>0.08</v>
+        <v>0.0565685424949238</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4442,7 +4387,7 @@
         <v>24.317326244402</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3629446749707</v>
+        <v>3</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -4459,29 +4404,29 @@
       <c r="X19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z19" t="e">
-        <v>#N/A</v>
+      <c r="Y19" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA19" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB19" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF19" t="e">
-        <v>#N/A</v>
+      <c r="AD19" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG19" t="e">
         <v>#N/A</v>
@@ -4489,21 +4434,21 @@
       <c r="AH19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI19" t="e">
-        <v>#N/A</v>
+      <c r="AI19" t="s">
+        <v>318</v>
       </c>
       <c r="AJ19" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4521,8 +4466,8 @@
       <c r="H20" t="n">
         <v>0.09965047</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.004</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4531,7 +4476,7 @@
         <v>#N/A</v>
       </c>
       <c r="L20" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M20" t="s">
         <v>275</v>
@@ -4540,7 +4485,7 @@
         <v>-24.8061967689132</v>
       </c>
       <c r="O20" t="n">
-        <v>0.30233014638419</v>
+        <v>0.213779696665382</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4552,7 +4497,7 @@
         <v>26.8233929125304</v>
       </c>
       <c r="S20" t="n">
-        <v>4.4731948463846</v>
+        <v>3</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -4569,29 +4514,29 @@
       <c r="X20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z20" t="e">
-        <v>#N/A</v>
+      <c r="Y20" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA20" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB20" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF20" t="e">
-        <v>#N/A</v>
+      <c r="AD20" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG20" t="e">
         <v>#N/A</v>
@@ -4599,21 +4544,21 @@
       <c r="AH20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI20" t="e">
-        <v>#N/A</v>
+      <c r="AI20" t="s">
+        <v>320</v>
       </c>
       <c r="AJ20" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4631,8 +4576,8 @@
       <c r="H21" t="n">
         <v>0.10005369</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.004</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4641,7 +4586,7 @@
         <v>#N/A</v>
       </c>
       <c r="L21" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M21" t="s">
         <v>275</v>
@@ -4650,7 +4595,7 @@
         <v>-25.1762340058953</v>
       </c>
       <c r="O21" t="n">
-        <v>0.554775231452652</v>
+        <v>0.392285328194507</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4662,7 +4607,7 @@
         <v>26.8726395457918</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4806621250915</v>
+        <v>3</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -4679,29 +4624,29 @@
       <c r="X21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z21" t="e">
-        <v>#N/A</v>
+      <c r="Y21" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA21" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB21" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" t="e">
-        <v>#N/A</v>
+      <c r="AD21" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG21" t="e">
         <v>#N/A</v>
@@ -4709,21 +4654,21 @@
       <c r="AH21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI21" t="e">
-        <v>#N/A</v>
+      <c r="AI21" t="s">
+        <v>322</v>
       </c>
       <c r="AJ21" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4741,8 +4686,8 @@
       <c r="H22" t="n">
         <v>0.10045691</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.004</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4751,7 +4696,7 @@
         <v>#N/A</v>
       </c>
       <c r="L22" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M22" t="s">
         <v>275</v>
@@ -4760,7 +4705,7 @@
         <v>-25.29</v>
       </c>
       <c r="O22" t="n">
-        <v>0.78</v>
+        <v>0.551543289325507</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4772,7 +4717,7 @@
         <v>26.9250121315814</v>
       </c>
       <c r="S22" t="n">
-        <v>4.5184818751849</v>
+        <v>3</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -4789,29 +4734,29 @@
       <c r="X22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z22" t="e">
-        <v>#N/A</v>
+      <c r="Y22" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA22" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB22" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#N/A</v>
+      <c r="AD22" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG22" t="e">
         <v>#N/A</v>
@@ -4819,21 +4764,21 @@
       <c r="AH22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI22" t="e">
-        <v>#N/A</v>
+      <c r="AI22" t="s">
+        <v>324</v>
       </c>
       <c r="AJ22" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4851,8 +4796,8 @@
       <c r="H23" t="n">
         <v>0.12477635</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.004</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4861,7 +4806,7 @@
         <v>#N/A</v>
       </c>
       <c r="L23" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M23" t="s">
         <v>275</v>
@@ -4870,7 +4815,7 @@
         <v>-24.51</v>
       </c>
       <c r="O23" t="n">
-        <v>0.58</v>
+        <v>0.410121933088197</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4882,7 +4827,7 @@
         <v>29.8947813003059</v>
       </c>
       <c r="S23" t="n">
-        <v>5.5421410915139</v>
+        <v>3</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -4899,29 +4844,29 @@
       <c r="X23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z23" t="e">
-        <v>#N/A</v>
+      <c r="Y23" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA23" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB23" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF23" t="e">
-        <v>#N/A</v>
+      <c r="AD23" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG23" t="e">
         <v>#N/A</v>
@@ -4929,21 +4874,21 @@
       <c r="AH23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI23" t="e">
-        <v>#N/A</v>
+      <c r="AI23" t="s">
+        <v>326</v>
       </c>
       <c r="AJ23" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4961,8 +4906,8 @@
       <c r="H24" t="n">
         <v>0.13750922</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.004</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4971,7 +4916,7 @@
         <v>#N/A</v>
       </c>
       <c r="L24" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M24" t="s">
         <v>275</v>
@@ -4980,7 +4925,7 @@
         <v>-24.98</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1</v>
+        <v>0.0707106781186548</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4992,7 +4937,7 @@
         <v>26.0067065559531</v>
       </c>
       <c r="S24" t="n">
-        <v>4.0421941213526</v>
+        <v>3</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -5009,29 +4954,29 @@
       <c r="X24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z24" t="e">
-        <v>#N/A</v>
+      <c r="Y24" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA24" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB24" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" t="e">
-        <v>#N/A</v>
+      <c r="AD24" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG24" t="e">
         <v>#N/A</v>
@@ -5039,21 +4984,21 @@
       <c r="AH24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI24" t="e">
-        <v>#N/A</v>
+      <c r="AI24" t="s">
+        <v>328</v>
       </c>
       <c r="AJ24" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -5071,8 +5016,8 @@
       <c r="H25" t="n">
         <v>0.15730934</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.004</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -5081,7 +5026,7 @@
         <v>#N/A</v>
       </c>
       <c r="L25" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M25" t="s">
         <v>275</v>
@@ -5090,7 +5035,7 @@
         <v>-23.3665787928722</v>
       </c>
       <c r="O25" t="n">
-        <v>0.140480061314442</v>
+        <v>0.0993344039769437</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -5102,7 +5047,7 @@
         <v>24.8571625302204</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5302557980721</v>
+        <v>3</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -5119,29 +5064,29 @@
       <c r="X25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" t="e">
-        <v>#N/A</v>
+      <c r="Y25" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA25" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB25" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#N/A</v>
+      <c r="AD25" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG25" t="e">
         <v>#N/A</v>
@@ -5149,21 +5094,21 @@
       <c r="AH25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI25" t="e">
-        <v>#N/A</v>
+      <c r="AI25" t="s">
+        <v>330</v>
       </c>
       <c r="AJ25" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -5181,8 +5126,8 @@
       <c r="H26" t="n">
         <v>0.15994936</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.004</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -5191,7 +5136,7 @@
         <v>#N/A</v>
       </c>
       <c r="L26" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M26" t="s">
         <v>275</v>
@@ -5200,7 +5145,7 @@
         <v>-23.8111118929164</v>
       </c>
       <c r="O26" t="n">
-        <v>1.32903970623076</v>
+        <v>0.939772988741944</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -5212,7 +5157,7 @@
         <v>26.1404428643064</v>
       </c>
       <c r="S26" t="n">
-        <v>4.1927760331553</v>
+        <v>3</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -5229,29 +5174,29 @@
       <c r="X26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z26" t="e">
-        <v>#N/A</v>
+      <c r="Y26" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB26" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF26" t="e">
-        <v>#N/A</v>
+      <c r="AD26" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG26" t="e">
         <v>#N/A</v>
@@ -5259,21 +5204,21 @@
       <c r="AH26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI26" t="e">
-        <v>#N/A</v>
+      <c r="AI26" t="s">
+        <v>332</v>
       </c>
       <c r="AJ26" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5291,8 +5236,8 @@
       <c r="H27" t="n">
         <v>0.18238949</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.004</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5301,7 +5246,7 @@
         <v>#N/A</v>
       </c>
       <c r="L27" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M27" t="s">
         <v>275</v>
@@ -5310,7 +5255,7 @@
         <v>-24.75</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -5322,7 +5267,7 @@
         <v>27.5641874716509</v>
       </c>
       <c r="S27" t="n">
-        <v>4.8091267152406</v>
+        <v>3</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
@@ -5339,29 +5284,29 @@
       <c r="X27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z27" t="e">
-        <v>#N/A</v>
+      <c r="Y27" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA27" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB27" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" t="e">
-        <v>#N/A</v>
+      <c r="AD27" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG27" t="e">
         <v>#N/A</v>
@@ -5369,21 +5314,21 @@
       <c r="AH27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI27" t="e">
-        <v>#N/A</v>
+      <c r="AI27" t="s">
+        <v>334</v>
       </c>
       <c r="AJ27" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5401,8 +5346,8 @@
       <c r="H28" t="n">
         <v>0.1837095</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.004</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5411,7 +5356,7 @@
         <v>#N/A</v>
       </c>
       <c r="L28" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M28" t="s">
         <v>275</v>
@@ -5420,7 +5365,7 @@
         <v>-25.45</v>
       </c>
       <c r="O28" t="n">
-        <v>0.06</v>
+        <v>0.0424264068711928</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5432,7 +5377,7 @@
         <v>26.6496698011663</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4395386094074</v>
+        <v>3</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
@@ -5449,29 +5394,29 @@
       <c r="X28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z28" t="e">
-        <v>#N/A</v>
+      <c r="Y28" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA28" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB28" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF28" t="e">
-        <v>#N/A</v>
+      <c r="AD28" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG28" t="e">
         <v>#N/A</v>
@@ -5479,21 +5424,21 @@
       <c r="AH28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI28" t="e">
-        <v>#N/A</v>
+      <c r="AI28" t="s">
+        <v>336</v>
       </c>
       <c r="AJ28" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5511,8 +5456,8 @@
       <c r="H29" t="n">
         <v>0.21670969</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.004</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5521,7 +5466,7 @@
         <v>#N/A</v>
       </c>
       <c r="L29" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M29" t="s">
         <v>275</v>
@@ -5530,7 +5475,7 @@
         <v>-25.93</v>
       </c>
       <c r="O29" t="n">
-        <v>0.38</v>
+        <v>0.268700576850888</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5542,7 +5487,7 @@
         <v>27.7851282520203</v>
       </c>
       <c r="S29" t="n">
-        <v>4.896221581473</v>
+        <v>3</v>
       </c>
       <c r="T29" t="e">
         <v>#N/A</v>
@@ -5559,29 +5504,29 @@
       <c r="X29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z29" t="e">
-        <v>#N/A</v>
+      <c r="Y29" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA29" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB29" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF29" t="e">
-        <v>#N/A</v>
+      <c r="AD29" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG29" t="e">
         <v>#N/A</v>
@@ -5589,21 +5534,21 @@
       <c r="AH29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI29" t="e">
-        <v>#N/A</v>
+      <c r="AI29" t="s">
+        <v>338</v>
       </c>
       <c r="AJ29" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5621,8 +5566,8 @@
       <c r="H30" t="n">
         <v>0.2180297</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.004</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5631,7 +5576,7 @@
         <v>#N/A</v>
       </c>
       <c r="L30" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M30" t="s">
         <v>275</v>
@@ -5640,7 +5585,7 @@
         <v>-25.33</v>
       </c>
       <c r="O30" t="n">
-        <v>0.24</v>
+        <v>0.169705627484771</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5652,7 +5597,7 @@
         <v>27.3040182707569</v>
       </c>
       <c r="S30" t="n">
-        <v>4.6959132273838</v>
+        <v>3</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -5669,29 +5614,29 @@
       <c r="X30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z30" t="e">
-        <v>#N/A</v>
+      <c r="Y30" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA30" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB30" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" t="e">
-        <v>#N/A</v>
+      <c r="AD30" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG30" t="e">
         <v>#N/A</v>
@@ -5699,21 +5644,21 @@
       <c r="AH30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI30" t="e">
-        <v>#N/A</v>
+      <c r="AI30" t="s">
+        <v>340</v>
       </c>
       <c r="AJ30" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5731,8 +5676,8 @@
       <c r="H31" t="n">
         <v>0.24100451</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.004</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5741,7 +5686,7 @@
         <v>#N/A</v>
       </c>
       <c r="L31" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s">
         <v>275</v>
@@ -5750,7 +5695,7 @@
         <v>-24.44</v>
       </c>
       <c r="O31" t="n">
-        <v>1.18</v>
+        <v>0.834386001800126</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5762,7 +5707,7 @@
         <v>26.7811881564485</v>
       </c>
       <c r="S31" t="n">
-        <v>4.4641703064084</v>
+        <v>3</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -5779,29 +5724,29 @@
       <c r="X31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z31" t="e">
-        <v>#N/A</v>
+      <c r="Y31" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA31" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB31" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#N/A</v>
+      <c r="AD31" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG31" t="e">
         <v>#N/A</v>
@@ -5809,21 +5754,21 @@
       <c r="AH31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI31" t="e">
-        <v>#N/A</v>
+      <c r="AI31" t="s">
+        <v>342</v>
       </c>
       <c r="AJ31" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5841,8 +5786,8 @@
       <c r="H32" t="n">
         <v>0.24388653</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.004</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5851,7 +5796,7 @@
         <v>#N/A</v>
       </c>
       <c r="L32" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M32" t="s">
         <v>275</v>
@@ -5860,7 +5805,7 @@
         <v>-24.67</v>
       </c>
       <c r="O32" t="n">
-        <v>0.42</v>
+        <v>0.29698484809835</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -5872,7 +5817,7 @@
         <v>27.4819586498228</v>
       </c>
       <c r="S32" t="n">
-        <v>4.7872883242637</v>
+        <v>3</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -5889,29 +5834,29 @@
       <c r="X32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z32" t="e">
-        <v>#N/A</v>
+      <c r="Y32" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA32" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB32" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF32" t="e">
-        <v>#N/A</v>
+      <c r="AD32" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG32" t="e">
         <v>#N/A</v>
@@ -5919,21 +5864,21 @@
       <c r="AH32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI32" t="e">
-        <v>#N/A</v>
+      <c r="AI32" t="s">
+        <v>344</v>
       </c>
       <c r="AJ32" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="B33" t="s">
         <v>271</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" t="s">
         <v>272</v>
       </c>
       <c r="D33" t="s">
@@ -5951,8 +5896,8 @@
       <c r="H33" t="n">
         <v>0.25321004</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.004</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -5961,7 +5906,7 @@
         <v>#N/A</v>
       </c>
       <c r="L33" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s">
         <v>275</v>
@@ -5970,7 +5915,7 @@
         <v>-24.98</v>
       </c>
       <c r="O33" t="n">
-        <v>0.52</v>
+        <v>0.367695526217005</v>
       </c>
       <c r="P33" t="e">
         <v>#N/A</v>
@@ -5982,7 +5927,7 @@
         <v>24.8286570921282</v>
       </c>
       <c r="S33" t="n">
-        <v>3.5129253865843</v>
+        <v>3</v>
       </c>
       <c r="T33" t="e">
         <v>#N/A</v>
@@ -5999,29 +5944,29 @@
       <c r="X33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z33" t="e">
-        <v>#N/A</v>
+      <c r="Y33" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA33" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB33" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF33" t="e">
-        <v>#N/A</v>
+      <c r="AD33" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG33" t="e">
         <v>#N/A</v>
@@ -6029,21 +5974,21 @@
       <c r="AH33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI33" t="e">
-        <v>#N/A</v>
+      <c r="AI33" t="s">
+        <v>346</v>
       </c>
       <c r="AJ33" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="B34" t="s">
         <v>271</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" t="s">
         <v>272</v>
       </c>
       <c r="D34" t="s">
@@ -6061,8 +6006,8 @@
       <c r="H34" t="n">
         <v>0.25452784</v>
       </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+      <c r="I34" t="n">
+        <v>0.004</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -6071,7 +6016,7 @@
         <v>#N/A</v>
       </c>
       <c r="L34" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M34" t="s">
         <v>275</v>
@@ -6080,7 +6025,7 @@
         <v>-25.3</v>
       </c>
       <c r="O34" t="n">
-        <v>0.7</v>
+        <v>0.494974746830583</v>
       </c>
       <c r="P34" t="e">
         <v>#N/A</v>
@@ -6092,7 +6037,7 @@
         <v>24.6002063302755</v>
       </c>
       <c r="S34" t="n">
-        <v>3.427139000128</v>
+        <v>3</v>
       </c>
       <c r="T34" t="e">
         <v>#N/A</v>
@@ -6109,29 +6054,29 @@
       <c r="X34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z34" t="e">
-        <v>#N/A</v>
+      <c r="Y34" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA34" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB34" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF34" t="e">
-        <v>#N/A</v>
+      <c r="AD34" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG34" t="e">
         <v>#N/A</v>
@@ -6139,21 +6084,21 @@
       <c r="AH34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI34" t="e">
-        <v>#N/A</v>
+      <c r="AI34" t="s">
+        <v>348</v>
       </c>
       <c r="AJ34" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="B35" t="s">
         <v>271</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" t="s">
         <v>272</v>
       </c>
       <c r="D35" t="s">
@@ -6171,8 +6116,8 @@
       <c r="H35" t="n">
         <v>0.26902366</v>
       </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+      <c r="I35" t="n">
+        <v>0.004</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -6181,7 +6126,7 @@
         <v>#N/A</v>
       </c>
       <c r="L35" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M35" t="s">
         <v>275</v>
@@ -6190,7 +6135,7 @@
         <v>-25.06</v>
       </c>
       <c r="O35" t="n">
-        <v>0.3</v>
+        <v>0.212132034355964</v>
       </c>
       <c r="P35" t="e">
         <v>#N/A</v>
@@ -6202,7 +6147,7 @@
         <v>24.7148437797699</v>
       </c>
       <c r="S35" t="n">
-        <v>3.4975351904814</v>
+        <v>3</v>
       </c>
       <c r="T35" t="e">
         <v>#N/A</v>
@@ -6219,29 +6164,29 @@
       <c r="X35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z35" t="e">
-        <v>#N/A</v>
+      <c r="Y35" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA35" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB35" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF35" t="e">
-        <v>#N/A</v>
+      <c r="AD35" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG35" t="e">
         <v>#N/A</v>
@@ -6249,21 +6194,21 @@
       <c r="AH35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI35" t="e">
-        <v>#N/A</v>
+      <c r="AI35" t="s">
+        <v>350</v>
       </c>
       <c r="AJ35" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s">
         <v>271</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" t="s">
         <v>272</v>
       </c>
       <c r="D36" t="s">
@@ -6281,8 +6226,8 @@
       <c r="H36" t="n">
         <v>0.29274409</v>
       </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+      <c r="I36" t="n">
+        <v>0.004</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -6291,7 +6236,7 @@
         <v>#N/A</v>
       </c>
       <c r="L36" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s">
         <v>275</v>
@@ -6300,7 +6245,7 @@
         <v>-24.07</v>
       </c>
       <c r="O36" t="n">
-        <v>0.08</v>
+        <v>0.0565685424949238</v>
       </c>
       <c r="P36" t="e">
         <v>#N/A</v>
@@ -6312,7 +6257,7 @@
         <v>28.0321765570932</v>
       </c>
       <c r="S36" t="n">
-        <v>4.9827926373886</v>
+        <v>3</v>
       </c>
       <c r="T36" t="e">
         <v>#N/A</v>
@@ -6329,29 +6274,29 @@
       <c r="X36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z36" t="e">
-        <v>#N/A</v>
+      <c r="Y36" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA36" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB36" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF36" t="e">
-        <v>#N/A</v>
+      <c r="AD36" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG36" t="e">
         <v>#N/A</v>
@@ -6359,21 +6304,21 @@
       <c r="AH36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI36" t="e">
-        <v>#N/A</v>
+      <c r="AI36" t="s">
+        <v>352</v>
       </c>
       <c r="AJ36" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s">
         <v>271</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" t="s">
         <v>272</v>
       </c>
       <c r="D37" t="s">
@@ -6391,8 +6336,8 @@
       <c r="H37" t="n">
         <v>0.3019687</v>
       </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+      <c r="I37" t="n">
+        <v>0.004</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -6401,7 +6346,7 @@
         <v>#N/A</v>
       </c>
       <c r="L37" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M37" t="s">
         <v>275</v>
@@ -6410,7 +6355,7 @@
         <v>-24.53</v>
       </c>
       <c r="O37" t="n">
-        <v>0.24</v>
+        <v>0.169705627484771</v>
       </c>
       <c r="P37" t="e">
         <v>#N/A</v>
@@ -6422,7 +6367,7 @@
         <v>27.185542746027</v>
       </c>
       <c r="S37" t="n">
-        <v>4.625271757272</v>
+        <v>3</v>
       </c>
       <c r="T37" t="e">
         <v>#N/A</v>
@@ -6439,29 +6384,29 @@
       <c r="X37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z37" t="e">
-        <v>#N/A</v>
+      <c r="Y37" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA37" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB37" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF37" t="e">
-        <v>#N/A</v>
+      <c r="AD37" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG37" t="e">
         <v>#N/A</v>
@@ -6473,17 +6418,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ37" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="B38" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="C38" t="s">
         <v>272</v>
       </c>
       <c r="D38" t="s">
@@ -6501,8 +6446,8 @@
       <c r="H38" t="n">
         <v>0.30855771</v>
       </c>
-      <c r="I38" t="e">
-        <v>#N/A</v>
+      <c r="I38" t="n">
+        <v>0.004</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -6511,7 +6456,7 @@
         <v>#N/A</v>
       </c>
       <c r="L38" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s">
         <v>275</v>
@@ -6520,7 +6465,7 @@
         <v>-25.53</v>
       </c>
       <c r="O38" t="n">
-        <v>0.12</v>
+        <v>0.0848528137423857</v>
       </c>
       <c r="P38" t="e">
         <v>#N/A</v>
@@ -6532,7 +6477,7 @@
         <v>28.7835765060275</v>
       </c>
       <c r="S38" t="n">
-        <v>5.1982478026947</v>
+        <v>3</v>
       </c>
       <c r="T38" t="e">
         <v>#N/A</v>
@@ -6549,29 +6494,29 @@
       <c r="X38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z38" t="e">
-        <v>#N/A</v>
+      <c r="Y38" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA38" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB38" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF38" t="e">
-        <v>#N/A</v>
+      <c r="AD38" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG38" t="e">
         <v>#N/A</v>
@@ -6579,21 +6524,21 @@
       <c r="AH38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI38" t="e">
-        <v>#N/A</v>
+      <c r="AI38" t="s">
+        <v>355</v>
       </c>
       <c r="AJ38" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s">
         <v>271</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" t="s">
         <v>272</v>
       </c>
       <c r="D39" t="s">
@@ -6611,8 +6556,8 @@
       <c r="H39" t="n">
         <v>0.34330865</v>
       </c>
-      <c r="I39" t="e">
-        <v>#N/A</v>
+      <c r="I39" t="n">
+        <v>0.004</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -6621,7 +6566,7 @@
         <v>#N/A</v>
       </c>
       <c r="L39" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M39" t="s">
         <v>275</v>
@@ -6630,7 +6575,7 @@
         <v>-25.25</v>
       </c>
       <c r="O39" t="n">
-        <v>0.04</v>
+        <v>0.0282842712474619</v>
       </c>
       <c r="P39" t="e">
         <v>#N/A</v>
@@ -6642,7 +6587,7 @@
         <v>26.150448201086</v>
       </c>
       <c r="S39" t="n">
-        <v>4.1228870109895</v>
+        <v>3</v>
       </c>
       <c r="T39" t="e">
         <v>#N/A</v>
@@ -6659,29 +6604,29 @@
       <c r="X39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z39" t="e">
-        <v>#N/A</v>
+      <c r="Y39" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA39" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB39" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF39" t="e">
-        <v>#N/A</v>
+      <c r="AD39" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG39" t="e">
         <v>#N/A</v>
@@ -6689,21 +6634,21 @@
       <c r="AH39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI39" t="e">
-        <v>#N/A</v>
+      <c r="AI39" t="s">
+        <v>357</v>
       </c>
       <c r="AJ39" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C40" t="s">
         <v>272</v>
       </c>
       <c r="D40" t="s">
@@ -6721,8 +6666,8 @@
       <c r="H40" t="n">
         <v>0.37637624</v>
       </c>
-      <c r="I40" t="e">
-        <v>#N/A</v>
+      <c r="I40" t="n">
+        <v>0.004</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -6731,7 +6676,7 @@
         <v>#N/A</v>
       </c>
       <c r="L40" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M40" t="s">
         <v>275</v>
@@ -6740,7 +6685,7 @@
         <v>-23.84</v>
       </c>
       <c r="O40" t="n">
-        <v>0.44</v>
+        <v>0.311126983722081</v>
       </c>
       <c r="P40" t="e">
         <v>#N/A</v>
@@ -6752,7 +6697,7 @@
         <v>26.2687837636731</v>
       </c>
       <c r="S40" t="n">
-        <v>4.2375184846969</v>
+        <v>3</v>
       </c>
       <c r="T40" t="e">
         <v>#N/A</v>
@@ -6769,29 +6714,29 @@
       <c r="X40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z40" t="e">
-        <v>#N/A</v>
+      <c r="Y40" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA40" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB40" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF40" t="e">
-        <v>#N/A</v>
+      <c r="AD40" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG40" t="e">
         <v>#N/A</v>
@@ -6803,17 +6748,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ40" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" t="s">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s">
         <v>271</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" t="s">
         <v>272</v>
       </c>
       <c r="D41" t="s">
@@ -6831,8 +6776,8 @@
       <c r="H41" t="n">
         <v>0.00198693</v>
       </c>
-      <c r="I41" t="e">
-        <v>#N/A</v>
+      <c r="I41" t="n">
+        <v>0.004</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -6841,7 +6786,7 @@
         <v>#N/A</v>
       </c>
       <c r="L41" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M41" t="s">
         <v>275</v>
@@ -6850,7 +6795,7 @@
         <v>-25.27</v>
       </c>
       <c r="O41" t="n">
-        <v>1.38</v>
+        <v>0.975807358037435</v>
       </c>
       <c r="P41" t="e">
         <v>#N/A</v>
@@ -6862,7 +6807,7 @@
         <v>26.4829987554541</v>
       </c>
       <c r="S41" t="n">
-        <v>4.3534288863418</v>
+        <v>3</v>
       </c>
       <c r="T41" t="e">
         <v>#N/A</v>
@@ -6879,29 +6824,29 @@
       <c r="X41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z41" t="e">
-        <v>#N/A</v>
+      <c r="Y41" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA41" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB41" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF41" t="e">
-        <v>#N/A</v>
+      <c r="AD41" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG41" t="e">
         <v>#N/A</v>
@@ -6913,17 +6858,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ41" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" t="s">
-        <v>332</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s">
         <v>271</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C42" t="s">
         <v>272</v>
       </c>
       <c r="D42" t="s">
@@ -6941,8 +6886,8 @@
       <c r="H42" t="n">
         <v>0.04083738889</v>
       </c>
-      <c r="I42" t="e">
-        <v>#N/A</v>
+      <c r="I42" t="n">
+        <v>0.004</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -6951,7 +6896,7 @@
         <v>#N/A</v>
       </c>
       <c r="L42" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M42" t="s">
         <v>275</v>
@@ -6960,7 +6905,7 @@
         <v>-23.87</v>
       </c>
       <c r="O42" t="n">
-        <v>0.88</v>
+        <v>0.622253967444162</v>
       </c>
       <c r="P42" t="e">
         <v>#N/A</v>
@@ -6972,7 +6917,7 @@
         <v>24.714504352348</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4687401757318</v>
+        <v>3</v>
       </c>
       <c r="T42" t="e">
         <v>#N/A</v>
@@ -6989,29 +6934,29 @@
       <c r="X42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z42" t="e">
-        <v>#N/A</v>
+      <c r="Y42" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA42" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB42" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF42" t="e">
-        <v>#N/A</v>
+      <c r="AD42" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG42" t="e">
         <v>#N/A</v>
@@ -7023,17 +6968,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ42" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s">
         <v>271</v>
       </c>
-      <c r="C43" s="34" t="s">
+      <c r="C43" t="s">
         <v>272</v>
       </c>
       <c r="D43" t="s">
@@ -7051,8 +6996,8 @@
       <c r="H43" t="n">
         <v>0.113572093</v>
       </c>
-      <c r="I43" t="e">
-        <v>#N/A</v>
+      <c r="I43" t="n">
+        <v>0.004</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -7061,7 +7006,7 @@
         <v>#N/A</v>
       </c>
       <c r="L43" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M43" t="s">
         <v>275</v>
@@ -7070,7 +7015,7 @@
         <v>-23.8</v>
       </c>
       <c r="O43" t="n">
-        <v>1.2</v>
+        <v>0.848528137423857</v>
       </c>
       <c r="P43" t="e">
         <v>#N/A</v>
@@ -7082,7 +7027,7 @@
         <v>28.38926817296</v>
       </c>
       <c r="S43" t="n">
-        <v>5.0238068414858</v>
+        <v>3</v>
       </c>
       <c r="T43" t="e">
         <v>#N/A</v>
@@ -7099,29 +7044,29 @@
       <c r="X43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z43" t="e">
-        <v>#N/A</v>
+      <c r="Y43" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA43" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB43" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF43" t="e">
-        <v>#N/A</v>
+      <c r="AD43" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG43" t="e">
         <v>#N/A</v>
@@ -7133,17 +7078,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ43" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s">
         <v>271</v>
       </c>
-      <c r="C44" s="34" t="s">
+      <c r="C44" t="s">
         <v>272</v>
       </c>
       <c r="D44" t="s">
@@ -7161,8 +7106,8 @@
       <c r="H44" t="n">
         <v>0.1232337454</v>
       </c>
-      <c r="I44" t="e">
-        <v>#N/A</v>
+      <c r="I44" t="n">
+        <v>0.004</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -7171,7 +7116,7 @@
         <v>#N/A</v>
       </c>
       <c r="L44" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M44" t="s">
         <v>275</v>
@@ -7180,7 +7125,7 @@
         <v>-25.16</v>
       </c>
       <c r="O44" t="n">
-        <v>1.36</v>
+        <v>0.961665222413705</v>
       </c>
       <c r="P44" t="e">
         <v>#N/A</v>
@@ -7192,7 +7137,7 @@
         <v>28.3976363570787</v>
       </c>
       <c r="S44" t="n">
-        <v>5.0727747369312</v>
+        <v>3</v>
       </c>
       <c r="T44" t="e">
         <v>#N/A</v>
@@ -7209,29 +7154,29 @@
       <c r="X44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z44" t="e">
-        <v>#N/A</v>
+      <c r="Y44" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA44" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB44" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF44" t="e">
-        <v>#N/A</v>
+      <c r="AD44" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG44" t="e">
         <v>#N/A</v>
@@ -7243,17 +7188,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ44" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="34" t="s">
+      <c r="C45" t="s">
         <v>272</v>
       </c>
       <c r="D45" t="s">
@@ -7271,8 +7216,8 @@
       <c r="H45" t="n">
         <v>0.128057612</v>
       </c>
-      <c r="I45" t="e">
-        <v>#N/A</v>
+      <c r="I45" t="n">
+        <v>0.004</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -7281,7 +7226,7 @@
         <v>#N/A</v>
       </c>
       <c r="L45" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s">
         <v>275</v>
@@ -7290,7 +7235,7 @@
         <v>-25.6</v>
       </c>
       <c r="O45" t="n">
-        <v>1.44</v>
+        <v>1.01823376490863</v>
       </c>
       <c r="P45" t="e">
         <v>#N/A</v>
@@ -7302,7 +7247,7 @@
         <v>27.8024049677921</v>
       </c>
       <c r="S45" t="n">
-        <v>4.8097537392232</v>
+        <v>3</v>
       </c>
       <c r="T45" t="e">
         <v>#N/A</v>
@@ -7319,29 +7264,29 @@
       <c r="X45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z45" t="e">
-        <v>#N/A</v>
+      <c r="Y45" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA45" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB45" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF45" t="e">
-        <v>#N/A</v>
+      <c r="AD45" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG45" t="e">
         <v>#N/A</v>
@@ -7353,17 +7298,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ45" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s">
         <v>271</v>
       </c>
-      <c r="C46" s="34" t="s">
+      <c r="C46" t="s">
         <v>272</v>
       </c>
       <c r="D46" t="s">
@@ -7381,8 +7326,8 @@
       <c r="H46" t="n">
         <v>0.136837314</v>
       </c>
-      <c r="I46" t="e">
-        <v>#N/A</v>
+      <c r="I46" t="n">
+        <v>0.004</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -7391,7 +7336,7 @@
         <v>#N/A</v>
       </c>
       <c r="L46" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M46" t="s">
         <v>275</v>
@@ -7400,7 +7345,7 @@
         <v>-24.24</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P46" t="e">
         <v>#N/A</v>
@@ -7412,7 +7357,7 @@
         <v>26.8419001125012</v>
       </c>
       <c r="S46" t="n">
-        <v>4.4892347070352</v>
+        <v>3</v>
       </c>
       <c r="T46" t="e">
         <v>#N/A</v>
@@ -7429,29 +7374,29 @@
       <c r="X46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z46" t="e">
-        <v>#N/A</v>
+      <c r="Y46" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA46" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB46" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF46" t="e">
-        <v>#N/A</v>
+      <c r="AD46" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG46" t="e">
         <v>#N/A</v>
@@ -7463,17 +7408,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ46" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s">
         <v>271</v>
       </c>
-      <c r="C47" s="34" t="s">
+      <c r="C47" t="s">
         <v>272</v>
       </c>
       <c r="D47" t="s">
@@ -7491,8 +7436,8 @@
       <c r="H47" t="n">
         <v>0.1385932544</v>
       </c>
-      <c r="I47" t="e">
-        <v>#N/A</v>
+      <c r="I47" t="n">
+        <v>0.004</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -7501,7 +7446,7 @@
         <v>#N/A</v>
       </c>
       <c r="L47" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M47" t="s">
         <v>275</v>
@@ -7510,7 +7455,7 @@
         <v>-23.99</v>
       </c>
       <c r="O47" t="n">
-        <v>0.52</v>
+        <v>0.367695526217005</v>
       </c>
       <c r="P47" t="e">
         <v>#N/A</v>
@@ -7522,7 +7467,7 @@
         <v>28.4414603941261</v>
       </c>
       <c r="S47" t="n">
-        <v>5.1084488374057</v>
+        <v>3</v>
       </c>
       <c r="T47" t="e">
         <v>#N/A</v>
@@ -7539,29 +7484,29 @@
       <c r="X47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z47" t="e">
-        <v>#N/A</v>
+      <c r="Y47" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA47" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB47" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF47" t="e">
-        <v>#N/A</v>
+      <c r="AD47" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG47" t="e">
         <v>#N/A</v>
@@ -7573,17 +7518,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ47" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s">
         <v>271</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="C48" t="s">
         <v>272</v>
       </c>
       <c r="D48" t="s">
@@ -7601,8 +7546,8 @@
       <c r="H48" t="n">
         <v>0.2009132809</v>
       </c>
-      <c r="I48" t="e">
-        <v>#N/A</v>
+      <c r="I48" t="n">
+        <v>0.004</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -7611,7 +7556,7 @@
         <v>#N/A</v>
       </c>
       <c r="L48" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M48" t="s">
         <v>275</v>
@@ -7620,7 +7565,7 @@
         <v>-24.83</v>
       </c>
       <c r="O48" t="n">
-        <v>0.3</v>
+        <v>0.212132034355964</v>
       </c>
       <c r="P48" t="e">
         <v>#N/A</v>
@@ -7632,7 +7577,7 @@
         <v>28.2760089702795</v>
       </c>
       <c r="S48" t="n">
-        <v>5.0559465429449</v>
+        <v>3</v>
       </c>
       <c r="T48" t="e">
         <v>#N/A</v>
@@ -7649,29 +7594,29 @@
       <c r="X48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z48" t="e">
-        <v>#N/A</v>
+      <c r="Y48" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA48" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB48" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF48" t="e">
-        <v>#N/A</v>
+      <c r="AD48" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG48" t="e">
         <v>#N/A</v>
@@ -7683,17 +7628,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ48" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="B49" t="s">
         <v>271</v>
       </c>
-      <c r="C49" s="34" t="s">
+      <c r="C49" t="s">
         <v>272</v>
       </c>
       <c r="D49" t="s">
@@ -7711,8 +7656,8 @@
       <c r="H49" t="n">
         <v>0.228526911</v>
       </c>
-      <c r="I49" t="e">
-        <v>#N/A</v>
+      <c r="I49" t="n">
+        <v>0.004</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -7721,7 +7666,7 @@
         <v>#N/A</v>
       </c>
       <c r="L49" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M49" t="s">
         <v>275</v>
@@ -7730,7 +7675,7 @@
         <v>-23.76</v>
       </c>
       <c r="O49" t="n">
-        <v>0.54</v>
+        <v>0.381837661840736</v>
       </c>
       <c r="P49" t="e">
         <v>#N/A</v>
@@ -7742,7 +7687,7 @@
         <v>24.8567726277264</v>
       </c>
       <c r="S49" t="n">
-        <v>3.5662043264142</v>
+        <v>3</v>
       </c>
       <c r="T49" t="e">
         <v>#N/A</v>
@@ -7759,29 +7704,29 @@
       <c r="X49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z49" t="e">
-        <v>#N/A</v>
+      <c r="Y49" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA49" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB49" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF49" t="e">
-        <v>#N/A</v>
+      <c r="AD49" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG49" t="e">
         <v>#N/A</v>
@@ -7793,17 +7738,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ49" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="B50" t="s">
         <v>271</v>
       </c>
-      <c r="C50" s="34" t="s">
+      <c r="C50" t="s">
         <v>272</v>
       </c>
       <c r="D50" t="s">
@@ -7821,8 +7766,8 @@
       <c r="H50" t="n">
         <v>0.2609115006</v>
       </c>
-      <c r="I50" t="e">
-        <v>#N/A</v>
+      <c r="I50" t="n">
+        <v>0.004</v>
       </c>
       <c r="J50" t="e">
         <v>#N/A</v>
@@ -7831,7 +7776,7 @@
         <v>#N/A</v>
       </c>
       <c r="L50" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M50" t="s">
         <v>275</v>
@@ -7840,7 +7785,7 @@
         <v>-23.07</v>
       </c>
       <c r="O50" t="n">
-        <v>0.74</v>
+        <v>0.523259018078045</v>
       </c>
       <c r="P50" t="e">
         <v>#N/A</v>
@@ -7852,7 +7797,7 @@
         <v>26.1047120946593</v>
       </c>
       <c r="S50" t="n">
-        <v>4.128012123182</v>
+        <v>3</v>
       </c>
       <c r="T50" t="e">
         <v>#N/A</v>
@@ -7869,29 +7814,29 @@
       <c r="X50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z50" t="e">
-        <v>#N/A</v>
+      <c r="Y50" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA50" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB50" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF50" t="e">
-        <v>#N/A</v>
+      <c r="AD50" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG50" t="e">
         <v>#N/A</v>
@@ -7903,17 +7848,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ50" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="B51" t="s">
         <v>271</v>
       </c>
-      <c r="C51" s="34" t="s">
+      <c r="C51" t="s">
         <v>272</v>
       </c>
       <c r="D51" t="s">
@@ -7931,8 +7876,8 @@
       <c r="H51" t="n">
         <v>0.3075195421</v>
       </c>
-      <c r="I51" t="e">
-        <v>#N/A</v>
+      <c r="I51" t="n">
+        <v>0.004</v>
       </c>
       <c r="J51" t="e">
         <v>#N/A</v>
@@ -7941,7 +7886,7 @@
         <v>#N/A</v>
       </c>
       <c r="L51" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s">
         <v>275</v>
@@ -7950,7 +7895,7 @@
         <v>-22.04</v>
       </c>
       <c r="O51" t="n">
-        <v>1.28</v>
+        <v>0.905096679918781</v>
       </c>
       <c r="P51" t="e">
         <v>#N/A</v>
@@ -7962,7 +7907,7 @@
         <v>27.7148066765272</v>
       </c>
       <c r="S51" t="n">
-        <v>4.7876502347416</v>
+        <v>3</v>
       </c>
       <c r="T51" t="e">
         <v>#N/A</v>
@@ -7979,29 +7924,29 @@
       <c r="X51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z51" t="e">
-        <v>#N/A</v>
+      <c r="Y51" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA51" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB51" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF51" t="e">
-        <v>#N/A</v>
+      <c r="AD51" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG51" t="e">
         <v>#N/A</v>
@@ -8013,17 +7958,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ51" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s">
         <v>271</v>
       </c>
-      <c r="C52" s="34" t="s">
+      <c r="C52" t="s">
         <v>272</v>
       </c>
       <c r="D52" t="s">
@@ -8041,8 +7986,8 @@
       <c r="H52" t="n">
         <v>0.3375755587</v>
       </c>
-      <c r="I52" t="e">
-        <v>#N/A</v>
+      <c r="I52" t="n">
+        <v>0.004</v>
       </c>
       <c r="J52" t="e">
         <v>#N/A</v>
@@ -8051,7 +7996,7 @@
         <v>#N/A</v>
       </c>
       <c r="L52" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M52" t="s">
         <v>275</v>
@@ -8060,7 +8005,7 @@
         <v>-23.21</v>
       </c>
       <c r="O52" t="n">
-        <v>0.38</v>
+        <v>0.268700576850888</v>
       </c>
       <c r="P52" t="e">
         <v>#N/A</v>
@@ -8072,7 +8017,7 @@
         <v>29.3766373896527</v>
       </c>
       <c r="S52" t="n">
-        <v>5.3851050163429</v>
+        <v>3</v>
       </c>
       <c r="T52" t="e">
         <v>#N/A</v>
@@ -8089,29 +8034,29 @@
       <c r="X52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z52" t="e">
-        <v>#N/A</v>
+      <c r="Y52" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA52" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB52" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF52" t="e">
-        <v>#N/A</v>
+      <c r="AD52" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG52" t="e">
         <v>#N/A</v>
@@ -8123,17 +8068,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ52" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" t="s">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s">
         <v>271</v>
       </c>
-      <c r="C53" s="34" t="s">
+      <c r="C53" t="s">
         <v>272</v>
       </c>
       <c r="D53" t="s">
@@ -8151,8 +8096,8 @@
       <c r="H53" t="n">
         <v>0.34837506</v>
       </c>
-      <c r="I53" t="e">
-        <v>#N/A</v>
+      <c r="I53" t="n">
+        <v>0.004</v>
       </c>
       <c r="J53" t="e">
         <v>#N/A</v>
@@ -8161,7 +8106,7 @@
         <v>#N/A</v>
       </c>
       <c r="L53" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M53" t="s">
         <v>275</v>
@@ -8170,7 +8115,7 @@
         <v>-22.92</v>
       </c>
       <c r="O53" t="n">
-        <v>0.76</v>
+        <v>0.537401153701776</v>
       </c>
       <c r="P53" t="e">
         <v>#N/A</v>
@@ -8182,7 +8127,7 @@
         <v>26.2113935011667</v>
       </c>
       <c r="S53" t="n">
-        <v>4.2008455339981</v>
+        <v>3</v>
       </c>
       <c r="T53" t="e">
         <v>#N/A</v>
@@ -8199,29 +8144,29 @@
       <c r="X53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z53" t="e">
-        <v>#N/A</v>
+      <c r="Y53" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA53" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB53" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF53" t="e">
-        <v>#N/A</v>
+      <c r="AD53" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG53" t="e">
         <v>#N/A</v>
@@ -8233,17 +8178,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ53" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
       <c r="A54" t="s">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="B54" t="s">
         <v>271</v>
       </c>
-      <c r="C54" s="34" t="s">
+      <c r="C54" t="s">
         <v>272</v>
       </c>
       <c r="D54" t="s">
@@ -8261,8 +8206,8 @@
       <c r="H54" t="n">
         <v>0.4030698368</v>
       </c>
-      <c r="I54" t="e">
-        <v>#N/A</v>
+      <c r="I54" t="n">
+        <v>0.004</v>
       </c>
       <c r="J54" t="e">
         <v>#N/A</v>
@@ -8271,7 +8216,7 @@
         <v>#N/A</v>
       </c>
       <c r="L54" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M54" t="s">
         <v>275</v>
@@ -8280,7 +8225,7 @@
         <v>-25.55</v>
       </c>
       <c r="O54" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P54" t="e">
         <v>#N/A</v>
@@ -8292,7 +8237,7 @@
         <v>27.0053316842041</v>
       </c>
       <c r="S54" t="n">
-        <v>4.5124704666244</v>
+        <v>3</v>
       </c>
       <c r="T54" t="e">
         <v>#N/A</v>
@@ -8309,29 +8254,29 @@
       <c r="X54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z54" t="e">
-        <v>#N/A</v>
+      <c r="Y54" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA54" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB54" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF54" t="e">
-        <v>#N/A</v>
+      <c r="AD54" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG54" t="e">
         <v>#N/A</v>
@@ -8343,17 +8288,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ54" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="B55" t="s">
         <v>271</v>
       </c>
-      <c r="C55" s="34" t="s">
+      <c r="C55" t="s">
         <v>272</v>
       </c>
       <c r="D55" t="s">
@@ -8371,8 +8316,8 @@
       <c r="H55" t="n">
         <v>0.4152791813</v>
       </c>
-      <c r="I55" t="e">
-        <v>#N/A</v>
+      <c r="I55" t="n">
+        <v>0.004</v>
       </c>
       <c r="J55" t="e">
         <v>#N/A</v>
@@ -8381,7 +8326,7 @@
         <v>#N/A</v>
       </c>
       <c r="L55" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M55" t="s">
         <v>275</v>
@@ -8390,7 +8335,7 @@
         <v>-22.6</v>
       </c>
       <c r="O55" t="n">
-        <v>0.1</v>
+        <v>0.0707106781186548</v>
       </c>
       <c r="P55" t="e">
         <v>#N/A</v>
@@ -8402,7 +8347,7 @@
         <v>28.3588733796524</v>
       </c>
       <c r="S55" t="n">
-        <v>5.0401644579988</v>
+        <v>3</v>
       </c>
       <c r="T55" t="e">
         <v>#N/A</v>
@@ -8419,29 +8364,29 @@
       <c r="X55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z55" t="e">
-        <v>#N/A</v>
+      <c r="Y55" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA55" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB55" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF55" t="e">
-        <v>#N/A</v>
+      <c r="AD55" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG55" t="e">
         <v>#N/A</v>
@@ -8453,17 +8398,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ55" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" t="s">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="B56" t="s">
         <v>271</v>
       </c>
-      <c r="C56" s="34" t="s">
+      <c r="C56" t="s">
         <v>272</v>
       </c>
       <c r="D56" t="s">
@@ -8481,8 +8426,8 @@
       <c r="H56" t="n">
         <v>0.4852723185</v>
       </c>
-      <c r="I56" t="e">
-        <v>#N/A</v>
+      <c r="I56" t="n">
+        <v>0.004</v>
       </c>
       <c r="J56" t="e">
         <v>#N/A</v>
@@ -8491,7 +8436,7 @@
         <v>#N/A</v>
       </c>
       <c r="L56" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M56" t="s">
         <v>275</v>
@@ -8500,7 +8445,7 @@
         <v>-23.09</v>
       </c>
       <c r="O56" t="n">
-        <v>1.04</v>
+        <v>0.735391052434009</v>
       </c>
       <c r="P56" t="e">
         <v>#N/A</v>
@@ -8512,7 +8457,7 @@
         <v>28.5428036715534</v>
       </c>
       <c r="S56" t="n">
-        <v>5.1376268240343</v>
+        <v>3</v>
       </c>
       <c r="T56" t="e">
         <v>#N/A</v>
@@ -8529,29 +8474,29 @@
       <c r="X56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z56" t="e">
-        <v>#N/A</v>
+      <c r="Y56" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA56" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB56" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF56" t="e">
-        <v>#N/A</v>
+      <c r="AD56" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG56" t="e">
         <v>#N/A</v>
@@ -8563,17 +8508,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ56" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="B57" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" t="s">
         <v>272</v>
       </c>
       <c r="D57" t="s">
@@ -8591,8 +8536,8 @@
       <c r="H57" t="n">
         <v>0.6162669419</v>
       </c>
-      <c r="I57" t="e">
-        <v>#N/A</v>
+      <c r="I57" t="n">
+        <v>0.004</v>
       </c>
       <c r="J57" t="e">
         <v>#N/A</v>
@@ -8601,7 +8546,7 @@
         <v>#N/A</v>
       </c>
       <c r="L57" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M57" t="s">
         <v>275</v>
@@ -8610,7 +8555,7 @@
         <v>-22.96</v>
       </c>
       <c r="O57" t="n">
-        <v>0.26</v>
+        <v>0.183847763108502</v>
       </c>
       <c r="P57" t="e">
         <v>#N/A</v>
@@ -8622,7 +8567,7 @@
         <v>29.630065683206</v>
       </c>
       <c r="S57" t="n">
-        <v>5.3989389539067</v>
+        <v>3</v>
       </c>
       <c r="T57" t="e">
         <v>#N/A</v>
@@ -8639,29 +8584,29 @@
       <c r="X57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z57" t="e">
-        <v>#N/A</v>
+      <c r="Y57" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA57" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB57" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF57" t="e">
-        <v>#N/A</v>
+      <c r="AD57" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG57" t="e">
         <v>#N/A</v>
@@ -8673,17 +8618,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ57" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="B58" t="s">
         <v>271</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" t="s">
         <v>272</v>
       </c>
       <c r="D58" t="s">
@@ -8701,8 +8646,8 @@
       <c r="H58" t="n">
         <v>0.6430777904</v>
       </c>
-      <c r="I58" t="e">
-        <v>#N/A</v>
+      <c r="I58" t="n">
+        <v>0.004</v>
       </c>
       <c r="J58" t="e">
         <v>#N/A</v>
@@ -8711,7 +8656,7 @@
         <v>#N/A</v>
       </c>
       <c r="L58" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M58" t="s">
         <v>275</v>
@@ -8720,7 +8665,7 @@
         <v>-24.33</v>
       </c>
       <c r="O58" t="n">
-        <v>1.42</v>
+        <v>1.0040916292849</v>
       </c>
       <c r="P58" t="e">
         <v>#N/A</v>
@@ -8732,7 +8677,7 @@
         <v>28.456925222539</v>
       </c>
       <c r="S58" t="n">
-        <v>5.0920796903762</v>
+        <v>3</v>
       </c>
       <c r="T58" t="e">
         <v>#N/A</v>
@@ -8749,29 +8694,29 @@
       <c r="X58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z58" t="e">
-        <v>#N/A</v>
+      <c r="Y58" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA58" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB58" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF58" t="e">
-        <v>#N/A</v>
+      <c r="AD58" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG58" t="e">
         <v>#N/A</v>
@@ -8783,17 +8728,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ58" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s">
         <v>271</v>
       </c>
-      <c r="C59" s="34" t="s">
+      <c r="C59" t="s">
         <v>272</v>
       </c>
       <c r="D59" t="s">
@@ -8811,8 +8756,8 @@
       <c r="H59" t="n">
         <v>0.7021715786</v>
       </c>
-      <c r="I59" t="e">
-        <v>#N/A</v>
+      <c r="I59" t="n">
+        <v>0.004</v>
       </c>
       <c r="J59" t="e">
         <v>#N/A</v>
@@ -8821,7 +8766,7 @@
         <v>#N/A</v>
       </c>
       <c r="L59" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M59" t="s">
         <v>275</v>
@@ -8830,7 +8775,7 @@
         <v>-25.27</v>
       </c>
       <c r="O59" t="n">
-        <v>0.52</v>
+        <v>0.367695526217005</v>
       </c>
       <c r="P59" t="e">
         <v>#N/A</v>
@@ -8842,7 +8787,7 @@
         <v>29.2955130964327</v>
       </c>
       <c r="S59" t="n">
-        <v>5.3316189880213</v>
+        <v>3</v>
       </c>
       <c r="T59" t="e">
         <v>#N/A</v>
@@ -8859,29 +8804,29 @@
       <c r="X59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z59" t="e">
-        <v>#N/A</v>
+      <c r="Y59" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA59" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB59" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF59" t="e">
-        <v>#N/A</v>
+      <c r="AD59" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG59" t="e">
         <v>#N/A</v>
@@ -8893,17 +8838,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ59" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" t="s">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="B60" t="s">
         <v>271</v>
       </c>
-      <c r="C60" s="34" t="s">
+      <c r="C60" t="s">
         <v>272</v>
       </c>
       <c r="D60" t="s">
@@ -8921,8 +8866,8 @@
       <c r="H60" t="n">
         <v>0.7074417171</v>
       </c>
-      <c r="I60" t="e">
-        <v>#N/A</v>
+      <c r="I60" t="n">
+        <v>0.004</v>
       </c>
       <c r="J60" t="e">
         <v>#N/A</v>
@@ -8931,7 +8876,7 @@
         <v>#N/A</v>
       </c>
       <c r="L60" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M60" t="s">
         <v>275</v>
@@ -8940,7 +8885,7 @@
         <v>-23.47</v>
       </c>
       <c r="O60" t="n">
-        <v>0.52</v>
+        <v>0.367695526217005</v>
       </c>
       <c r="P60" t="e">
         <v>#N/A</v>
@@ -8952,7 +8897,7 @@
         <v>28.6871477013305</v>
       </c>
       <c r="S60" t="n">
-        <v>5.1248978257715</v>
+        <v>3</v>
       </c>
       <c r="T60" t="e">
         <v>#N/A</v>
@@ -8969,29 +8914,29 @@
       <c r="X60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z60" t="e">
-        <v>#N/A</v>
+      <c r="Y60" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA60" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB60" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF60" t="e">
-        <v>#N/A</v>
+      <c r="AD60" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG60" t="e">
         <v>#N/A</v>
@@ -9003,17 +8948,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ60" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="B61" t="s">
         <v>271</v>
       </c>
-      <c r="C61" s="34" t="s">
+      <c r="C61" t="s">
         <v>272</v>
       </c>
       <c r="D61" t="s">
@@ -9031,8 +8976,8 @@
       <c r="H61" t="n">
         <v>0.7212109903</v>
       </c>
-      <c r="I61" t="e">
-        <v>#N/A</v>
+      <c r="I61" t="n">
+        <v>0.004</v>
       </c>
       <c r="J61" t="e">
         <v>#N/A</v>
@@ -9041,7 +8986,7 @@
         <v>#N/A</v>
       </c>
       <c r="L61" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M61" t="s">
         <v>275</v>
@@ -9050,7 +8995,7 @@
         <v>-23.29</v>
       </c>
       <c r="O61" t="n">
-        <v>0.74</v>
+        <v>0.523259018078045</v>
       </c>
       <c r="P61" t="e">
         <v>#N/A</v>
@@ -9062,7 +9007,7 @@
         <v>27.662405114285</v>
       </c>
       <c r="S61" t="n">
-        <v>4.8352499280151</v>
+        <v>3</v>
       </c>
       <c r="T61" t="e">
         <v>#N/A</v>
@@ -9079,29 +9024,29 @@
       <c r="X61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z61" t="e">
-        <v>#N/A</v>
+      <c r="Y61" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA61" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB61" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF61" t="e">
-        <v>#N/A</v>
+      <c r="AD61" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG61" t="e">
         <v>#N/A</v>
@@ -9113,17 +9058,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ61" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" t="s">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="B62" t="s">
         <v>271</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="C62" t="s">
         <v>272</v>
       </c>
       <c r="D62" t="s">
@@ -9141,8 +9086,8 @@
       <c r="H62" t="n">
         <v>0.7894617602</v>
       </c>
-      <c r="I62" t="e">
-        <v>#N/A</v>
+      <c r="I62" t="n">
+        <v>0.004</v>
       </c>
       <c r="J62" t="e">
         <v>#N/A</v>
@@ -9151,7 +9096,7 @@
         <v>#N/A</v>
       </c>
       <c r="L62" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M62" t="s">
         <v>275</v>
@@ -9160,7 +9105,7 @@
         <v>-23.99</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P62" t="e">
         <v>#N/A</v>
@@ -9172,7 +9117,7 @@
         <v>27.2579582787662</v>
       </c>
       <c r="S62" t="n">
-        <v>4.6977176291609</v>
+        <v>3</v>
       </c>
       <c r="T62" t="e">
         <v>#N/A</v>
@@ -9189,29 +9134,29 @@
       <c r="X62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z62" t="e">
-        <v>#N/A</v>
+      <c r="Y62" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.108</v>
       </c>
       <c r="AA62" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB62" t="e">
-        <v>#N/A</v>
+        <v>314</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF62" t="e">
-        <v>#N/A</v>
+      <c r="AD62" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG62" t="e">
         <v>#N/A</v>
@@ -9223,2428 +9168,96 @@
         <v>#N/A</v>
       </c>
       <c r="AJ62" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
-      <c r="A63" t="s">
-        <v>353</v>
-      </c>
-      <c r="B63" t="s">
-        <v>271</v>
-      </c>
-      <c r="C63" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D63" t="s">
-        <v>273</v>
-      </c>
-      <c r="E63" t="s">
-        <v>274</v>
-      </c>
-      <c r="F63" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G63" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="I63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L63" t="s">
-        <v>354</v>
-      </c>
-      <c r="M63" t="s">
-        <v>275</v>
-      </c>
-      <c r="N63" t="n">
-        <v>-26.7514595618863</v>
-      </c>
-      <c r="O63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R63" s="11" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V63" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA63" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI63" t="s">
-        <v>355</v>
-      </c>
-      <c r="AJ63" t="s">
-        <v>279</v>
-      </c>
+      <c r="R63" s="11"/>
+      <c r="V63" s="11"/>
     </row>
     <row r="64" ht="19" customHeight="1">
-      <c r="A64" t="s">
-        <v>356</v>
-      </c>
-      <c r="B64" t="s">
-        <v>271</v>
-      </c>
-      <c r="C64" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D64" t="s">
-        <v>273</v>
-      </c>
-      <c r="E64" t="s">
-        <v>274</v>
-      </c>
-      <c r="F64" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G64" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.0085</v>
-      </c>
-      <c r="I64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L64" t="s">
-        <v>354</v>
-      </c>
-      <c r="M64" t="s">
-        <v>275</v>
-      </c>
-      <c r="N64" t="n">
-        <v>-25.9645212931048</v>
-      </c>
-      <c r="O64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R64" s="11" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V64" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA64" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI64" t="s">
-        <v>357</v>
-      </c>
-      <c r="AJ64" t="s">
-        <v>279</v>
-      </c>
+      <c r="R64" s="11"/>
+      <c r="V64" s="11"/>
     </row>
     <row r="65" ht="19" customHeight="1">
-      <c r="A65" t="s">
-        <v>358</v>
-      </c>
-      <c r="B65" t="s">
-        <v>271</v>
-      </c>
-      <c r="C65" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D65" t="s">
-        <v>273</v>
-      </c>
-      <c r="E65" t="s">
-        <v>274</v>
-      </c>
-      <c r="F65" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G65" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.0151</v>
-      </c>
-      <c r="I65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L65" t="s">
-        <v>354</v>
-      </c>
-      <c r="M65" t="s">
-        <v>275</v>
-      </c>
-      <c r="N65" t="n">
-        <v>-26.4328879232892</v>
-      </c>
-      <c r="O65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R65" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="S65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V65" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA65" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI65" t="s">
-        <v>359</v>
-      </c>
-      <c r="AJ65" t="s">
-        <v>279</v>
-      </c>
+      <c r="R65" s="11"/>
+      <c r="V65" s="11"/>
     </row>
     <row r="66" ht="19" customHeight="1">
-      <c r="A66" t="s">
-        <v>360</v>
-      </c>
-      <c r="B66" t="s">
-        <v>271</v>
-      </c>
-      <c r="C66" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D66" t="s">
-        <v>273</v>
-      </c>
-      <c r="E66" t="s">
-        <v>274</v>
-      </c>
-      <c r="F66" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G66" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="I66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L66" t="s">
-        <v>354</v>
-      </c>
-      <c r="M66" t="s">
-        <v>275</v>
-      </c>
-      <c r="N66" t="n">
-        <v>-24.3657399088488</v>
-      </c>
-      <c r="O66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R66" s="11" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="S66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V66" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA66" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI66" t="s">
-        <v>361</v>
-      </c>
-      <c r="AJ66" t="s">
-        <v>279</v>
-      </c>
+      <c r="R66" s="11"/>
+      <c r="V66" s="11"/>
     </row>
     <row r="67" ht="19" customHeight="1">
-      <c r="A67" t="s">
-        <v>362</v>
-      </c>
-      <c r="B67" t="s">
-        <v>271</v>
-      </c>
-      <c r="C67" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D67" t="s">
-        <v>273</v>
-      </c>
-      <c r="E67" t="s">
-        <v>274</v>
-      </c>
-      <c r="F67" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G67" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.0174</v>
-      </c>
-      <c r="I67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L67" t="s">
-        <v>354</v>
-      </c>
-      <c r="M67" t="s">
-        <v>275</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-23.8836630347779</v>
-      </c>
-      <c r="O67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R67" s="11" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="S67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V67" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA67" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI67" t="s">
-        <v>363</v>
-      </c>
-      <c r="AJ67" t="s">
-        <v>279</v>
-      </c>
+      <c r="R67" s="11"/>
+      <c r="V67" s="11"/>
     </row>
     <row r="68" ht="19" customHeight="1">
-      <c r="A68" t="s">
-        <v>364</v>
-      </c>
-      <c r="B68" t="s">
-        <v>271</v>
-      </c>
-      <c r="C68" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D68" t="s">
-        <v>273</v>
-      </c>
-      <c r="E68" t="s">
-        <v>274</v>
-      </c>
-      <c r="F68" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G68" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.0178</v>
-      </c>
-      <c r="I68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L68" t="s">
-        <v>354</v>
-      </c>
-      <c r="M68" t="s">
-        <v>275</v>
-      </c>
-      <c r="N68" t="n">
-        <v>-24.5684091020468</v>
-      </c>
-      <c r="O68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R68" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="S68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V68" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA68" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI68" t="s">
-        <v>365</v>
-      </c>
-      <c r="AJ68" t="s">
-        <v>279</v>
-      </c>
+      <c r="R68" s="11"/>
+      <c r="V68" s="11"/>
     </row>
     <row r="69" ht="19" customHeight="1">
-      <c r="A69" t="s">
-        <v>366</v>
-      </c>
-      <c r="B69" t="s">
-        <v>271</v>
-      </c>
-      <c r="C69" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D69" t="s">
-        <v>273</v>
-      </c>
-      <c r="E69" t="s">
-        <v>274</v>
-      </c>
-      <c r="F69" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G69" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.0191</v>
-      </c>
-      <c r="I69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L69" t="s">
-        <v>354</v>
-      </c>
-      <c r="M69" t="s">
-        <v>275</v>
-      </c>
-      <c r="N69" t="n">
-        <v>-21.4106048973324</v>
-      </c>
-      <c r="O69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R69" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V69" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA69" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI69" t="s">
-        <v>367</v>
-      </c>
-      <c r="AJ69" t="s">
-        <v>279</v>
-      </c>
+      <c r="R69" s="11"/>
+      <c r="V69" s="11"/>
     </row>
     <row r="70" ht="19" customHeight="1">
-      <c r="A70" t="s">
-        <v>368</v>
-      </c>
-      <c r="B70" t="s">
-        <v>271</v>
-      </c>
-      <c r="C70" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D70" t="s">
-        <v>273</v>
-      </c>
-      <c r="E70" t="s">
-        <v>274</v>
-      </c>
-      <c r="F70" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G70" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.0267</v>
-      </c>
-      <c r="I70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L70" t="s">
-        <v>354</v>
-      </c>
-      <c r="M70" t="s">
-        <v>275</v>
-      </c>
-      <c r="N70" t="n">
-        <v>-23.4640083636898</v>
-      </c>
-      <c r="O70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R70" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="S70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V70" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA70" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI70" t="s">
-        <v>369</v>
-      </c>
-      <c r="AJ70" t="s">
-        <v>279</v>
-      </c>
+      <c r="R70" s="11"/>
+      <c r="V70" s="11"/>
     </row>
     <row r="71" ht="19" customHeight="1">
-      <c r="A71" t="s">
-        <v>370</v>
-      </c>
-      <c r="B71" t="s">
-        <v>271</v>
-      </c>
-      <c r="C71" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D71" t="s">
-        <v>273</v>
-      </c>
-      <c r="E71" t="s">
-        <v>274</v>
-      </c>
-      <c r="F71" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G71" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.0339</v>
-      </c>
-      <c r="I71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L71" t="s">
-        <v>354</v>
-      </c>
-      <c r="M71" t="s">
-        <v>275</v>
-      </c>
-      <c r="N71" t="n">
-        <v>-23.9576571867291</v>
-      </c>
-      <c r="O71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R71" s="11" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="S71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V71" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA71" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI71" t="s">
-        <v>371</v>
-      </c>
-      <c r="AJ71" t="s">
-        <v>279</v>
-      </c>
+      <c r="R71" s="11"/>
+      <c r="V71" s="11"/>
     </row>
     <row r="72" ht="19" customHeight="1">
-      <c r="A72" t="s">
-        <v>372</v>
-      </c>
-      <c r="B72" t="s">
-        <v>271</v>
-      </c>
-      <c r="C72" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D72" t="s">
-        <v>273</v>
-      </c>
-      <c r="E72" t="s">
-        <v>274</v>
-      </c>
-      <c r="F72" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G72" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.0462</v>
-      </c>
-      <c r="I72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L72" t="s">
-        <v>354</v>
-      </c>
-      <c r="M72" t="s">
-        <v>275</v>
-      </c>
-      <c r="N72" t="n">
-        <v>-23.4615498962706</v>
-      </c>
-      <c r="O72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R72" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V72" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA72" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI72" t="s">
-        <v>373</v>
-      </c>
-      <c r="AJ72" t="s">
-        <v>279</v>
-      </c>
+      <c r="R72" s="11"/>
+      <c r="V72" s="11"/>
     </row>
     <row r="73" ht="19" customHeight="1">
-      <c r="A73" t="s">
-        <v>374</v>
-      </c>
-      <c r="B73" t="s">
-        <v>271</v>
-      </c>
-      <c r="C73" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D73" t="s">
-        <v>273</v>
-      </c>
-      <c r="E73" t="s">
-        <v>274</v>
-      </c>
-      <c r="F73" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G73" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.0573</v>
-      </c>
-      <c r="I73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L73" t="s">
-        <v>354</v>
-      </c>
-      <c r="M73" t="s">
-        <v>275</v>
-      </c>
-      <c r="N73" t="n">
-        <v>-24.3604913667771</v>
-      </c>
-      <c r="O73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R73" s="11" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V73" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA73" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI73" t="s">
-        <v>375</v>
-      </c>
-      <c r="AJ73" t="s">
-        <v>279</v>
-      </c>
+      <c r="R73" s="11"/>
+      <c r="V73" s="11"/>
     </row>
     <row r="74" ht="19" customHeight="1">
-      <c r="A74" t="s">
-        <v>376</v>
-      </c>
-      <c r="B74" t="s">
-        <v>271</v>
-      </c>
-      <c r="C74" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D74" t="s">
-        <v>273</v>
-      </c>
-      <c r="E74" t="s">
-        <v>274</v>
-      </c>
-      <c r="F74" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G74" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.0601</v>
-      </c>
-      <c r="I74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L74" t="s">
-        <v>354</v>
-      </c>
-      <c r="M74" t="s">
-        <v>275</v>
-      </c>
-      <c r="N74" t="n">
-        <v>-22.8637649672476</v>
-      </c>
-      <c r="O74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R74" s="11" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V74" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA74" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI74" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ74" t="s">
-        <v>279</v>
-      </c>
+      <c r="R74" s="11"/>
+      <c r="V74" s="11"/>
     </row>
     <row r="75" ht="19" customHeight="1">
-      <c r="A75" t="s">
-        <v>378</v>
-      </c>
-      <c r="B75" t="s">
-        <v>271</v>
-      </c>
-      <c r="C75" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D75" t="s">
-        <v>273</v>
-      </c>
-      <c r="E75" t="s">
-        <v>274</v>
-      </c>
-      <c r="F75" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G75" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.0618</v>
-      </c>
-      <c r="I75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L75" t="s">
-        <v>354</v>
-      </c>
-      <c r="M75" t="s">
-        <v>275</v>
-      </c>
-      <c r="N75" t="n">
-        <v>-24.8925380204844</v>
-      </c>
-      <c r="O75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R75" s="11" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V75" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA75" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI75" t="s">
-        <v>379</v>
-      </c>
-      <c r="AJ75" t="s">
-        <v>279</v>
-      </c>
+      <c r="R75" s="11"/>
+      <c r="V75" s="11"/>
     </row>
     <row r="76" ht="19" customHeight="1">
-      <c r="A76" t="s">
-        <v>380</v>
-      </c>
-      <c r="B76" t="s">
-        <v>271</v>
-      </c>
-      <c r="C76" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D76" t="s">
-        <v>273</v>
-      </c>
-      <c r="E76" t="s">
-        <v>274</v>
-      </c>
-      <c r="F76" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G76" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.0659</v>
-      </c>
-      <c r="I76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L76" t="s">
-        <v>354</v>
-      </c>
-      <c r="M76" t="s">
-        <v>275</v>
-      </c>
-      <c r="N76" t="n">
-        <v>-24.7652122776352</v>
-      </c>
-      <c r="O76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R76" s="11" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="S76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V76" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA76" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI76" t="s">
-        <v>381</v>
-      </c>
-      <c r="AJ76" t="s">
-        <v>279</v>
-      </c>
+      <c r="R76" s="11"/>
+      <c r="V76" s="11"/>
     </row>
     <row r="77" ht="19" customHeight="1">
-      <c r="A77" t="s">
-        <v>382</v>
-      </c>
-      <c r="B77" t="s">
-        <v>271</v>
-      </c>
-      <c r="C77" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D77" t="s">
-        <v>273</v>
-      </c>
-      <c r="E77" t="s">
-        <v>274</v>
-      </c>
-      <c r="F77" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G77" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.072</v>
-      </c>
-      <c r="I77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L77" t="s">
-        <v>354</v>
-      </c>
-      <c r="M77" t="s">
-        <v>275</v>
-      </c>
-      <c r="N77" t="n">
-        <v>-23.3060947122531</v>
-      </c>
-      <c r="O77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R77" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V77" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA77" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI77" t="s">
-        <v>383</v>
-      </c>
-      <c r="AJ77" t="s">
-        <v>279</v>
-      </c>
+      <c r="R77" s="11"/>
+      <c r="V77" s="11"/>
     </row>
     <row r="78" ht="19" customHeight="1">
-      <c r="A78" t="s">
-        <v>384</v>
-      </c>
-      <c r="B78" t="s">
-        <v>271</v>
-      </c>
-      <c r="C78" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D78" t="s">
-        <v>273</v>
-      </c>
-      <c r="E78" t="s">
-        <v>274</v>
-      </c>
-      <c r="F78" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G78" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.0802</v>
-      </c>
-      <c r="I78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L78" t="s">
-        <v>354</v>
-      </c>
-      <c r="M78" t="s">
-        <v>275</v>
-      </c>
-      <c r="N78" t="n">
-        <v>-24.8394579936945</v>
-      </c>
-      <c r="O78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R78" s="11" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="S78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V78" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W78" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA78" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI78" t="s">
-        <v>385</v>
-      </c>
-      <c r="AJ78" t="s">
-        <v>279</v>
-      </c>
+      <c r="R78" s="11"/>
+      <c r="V78" s="11"/>
     </row>
     <row r="79" ht="19" customHeight="1">
-      <c r="A79" t="s">
-        <v>386</v>
-      </c>
-      <c r="B79" t="s">
-        <v>271</v>
-      </c>
-      <c r="C79" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D79" t="s">
-        <v>273</v>
-      </c>
-      <c r="E79" t="s">
-        <v>274</v>
-      </c>
-      <c r="F79" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G79" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.0815</v>
-      </c>
-      <c r="I79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L79" t="s">
-        <v>354</v>
-      </c>
-      <c r="M79" t="s">
-        <v>275</v>
-      </c>
-      <c r="N79" t="n">
-        <v>-24.1418364179884</v>
-      </c>
-      <c r="O79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R79" s="11" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V79" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA79" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI79" t="s">
-        <v>387</v>
-      </c>
-      <c r="AJ79" t="s">
-        <v>279</v>
-      </c>
+      <c r="R79" s="11"/>
+      <c r="V79" s="11"/>
     </row>
     <row r="80" ht="19" customHeight="1">
-      <c r="A80" t="s">
-        <v>388</v>
-      </c>
-      <c r="B80" t="s">
-        <v>271</v>
-      </c>
-      <c r="C80" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D80" t="s">
-        <v>273</v>
-      </c>
-      <c r="E80" t="s">
-        <v>274</v>
-      </c>
-      <c r="F80" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G80" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.0829</v>
-      </c>
-      <c r="I80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L80" t="s">
-        <v>354</v>
-      </c>
-      <c r="M80" t="s">
-        <v>275</v>
-      </c>
-      <c r="N80" t="n">
-        <v>-24.0655667543329</v>
-      </c>
-      <c r="O80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R80" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V80" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA80" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI80" t="s">
-        <v>389</v>
-      </c>
-      <c r="AJ80" t="s">
-        <v>279</v>
-      </c>
+      <c r="R80" s="11"/>
+      <c r="V80" s="11"/>
     </row>
     <row r="81" ht="19" customHeight="1">
-      <c r="A81" t="s">
-        <v>390</v>
-      </c>
-      <c r="B81" t="s">
-        <v>271</v>
-      </c>
-      <c r="C81" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D81" t="s">
-        <v>273</v>
-      </c>
-      <c r="E81" t="s">
-        <v>274</v>
-      </c>
-      <c r="F81" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G81" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.0918</v>
-      </c>
-      <c r="I81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L81" t="s">
-        <v>354</v>
-      </c>
-      <c r="M81" t="s">
-        <v>275</v>
-      </c>
-      <c r="N81" t="n">
-        <v>-23.4303673816096</v>
-      </c>
-      <c r="O81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R81" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V81" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA81" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI81" t="s">
-        <v>391</v>
-      </c>
-      <c r="AJ81" t="s">
-        <v>279</v>
-      </c>
+      <c r="R81" s="11"/>
+      <c r="V81" s="11"/>
     </row>
     <row r="82" ht="19" customHeight="1">
-      <c r="A82" t="s">
-        <v>392</v>
-      </c>
-      <c r="B82" t="s">
-        <v>271</v>
-      </c>
-      <c r="C82" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D82" t="s">
-        <v>273</v>
-      </c>
-      <c r="E82" t="s">
-        <v>274</v>
-      </c>
-      <c r="F82" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G82" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.09311</v>
-      </c>
-      <c r="I82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L82" t="s">
-        <v>354</v>
-      </c>
-      <c r="M82" t="s">
-        <v>275</v>
-      </c>
-      <c r="N82" t="n">
-        <v>-24.3686328960909</v>
-      </c>
-      <c r="O82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R82" s="11" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="S82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V82" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA82" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI82" t="s">
-        <v>393</v>
-      </c>
-      <c r="AJ82" t="s">
-        <v>279</v>
-      </c>
+      <c r="R82" s="11"/>
+      <c r="V82" s="11"/>
     </row>
     <row r="83" ht="19" customHeight="1">
-      <c r="A83" t="s">
-        <v>394</v>
-      </c>
-      <c r="B83" t="s">
-        <v>271</v>
-      </c>
-      <c r="C83" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D83" t="s">
-        <v>273</v>
-      </c>
-      <c r="E83" t="s">
-        <v>274</v>
-      </c>
-      <c r="F83" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G83" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.0939</v>
-      </c>
-      <c r="I83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L83" t="s">
-        <v>354</v>
-      </c>
-      <c r="M83" t="s">
-        <v>275</v>
-      </c>
-      <c r="N83" t="n">
-        <v>-25.7888151983925</v>
-      </c>
-      <c r="O83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R83" s="11" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V83" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA83" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI83" t="s">
-        <v>395</v>
-      </c>
-      <c r="AJ83" t="s">
-        <v>279</v>
-      </c>
+      <c r="R83" s="11"/>
+      <c r="V83" s="11"/>
     </row>
     <row r="84" ht="19" customHeight="1">
-      <c r="A84" t="s">
-        <v>396</v>
-      </c>
-      <c r="B84" t="s">
-        <v>271</v>
-      </c>
-      <c r="C84" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D84" t="s">
-        <v>273</v>
-      </c>
-      <c r="E84" t="s">
-        <v>274</v>
-      </c>
-      <c r="F84" t="n">
-        <v>27.1935</v>
-      </c>
-      <c r="G84" t="n">
-        <v>-91.409</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="I84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L84" t="s">
-        <v>354</v>
-      </c>
-      <c r="M84" t="s">
-        <v>275</v>
-      </c>
-      <c r="N84" t="n">
-        <v>-25.7631899635722</v>
-      </c>
-      <c r="O84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R84" s="11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V84" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="W84" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA84" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI84" t="s">
-        <v>397</v>
-      </c>
-      <c r="AJ84" t="s">
-        <v>279</v>
-      </c>
+      <c r="R84" s="11"/>
+      <c r="V84" s="11"/>
     </row>
     <row r="85" ht="19" customHeight="1">
       <c r="R85" s="11"/>
@@ -11740,88 +9353,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-    <hyperlink ref="C52" r:id="rId48h"/>
-    <hyperlink ref="C53" r:id="rId49h"/>
-    <hyperlink ref="C54" r:id="rId50h"/>
-    <hyperlink ref="C55" r:id="rId51h"/>
-    <hyperlink ref="C56" r:id="rId52h"/>
-    <hyperlink ref="C57" r:id="rId53h"/>
-    <hyperlink ref="C58" r:id="rId54h"/>
-    <hyperlink ref="C59" r:id="rId55h"/>
-    <hyperlink ref="C60" r:id="rId56h"/>
-    <hyperlink ref="C61" r:id="rId57h"/>
-    <hyperlink ref="C62" r:id="rId58h"/>
-    <hyperlink ref="C63" r:id="rId59h"/>
-    <hyperlink ref="C64" r:id="rId60h"/>
-    <hyperlink ref="C65" r:id="rId61h"/>
-    <hyperlink ref="C66" r:id="rId62h"/>
-    <hyperlink ref="C67" r:id="rId63h"/>
-    <hyperlink ref="C68" r:id="rId64h"/>
-    <hyperlink ref="C69" r:id="rId65h"/>
-    <hyperlink ref="C70" r:id="rId66h"/>
-    <hyperlink ref="C71" r:id="rId67h"/>
-    <hyperlink ref="C72" r:id="rId68h"/>
-    <hyperlink ref="C73" r:id="rId69h"/>
-    <hyperlink ref="C74" r:id="rId70h"/>
-    <hyperlink ref="C75" r:id="rId71h"/>
-    <hyperlink ref="C76" r:id="rId72h"/>
-    <hyperlink ref="C77" r:id="rId73h"/>
-    <hyperlink ref="C78" r:id="rId74h"/>
-    <hyperlink ref="C79" r:id="rId75h"/>
-    <hyperlink ref="C80" r:id="rId76h"/>
-    <hyperlink ref="C81" r:id="rId77h"/>
-    <hyperlink ref="C82" r:id="rId78h"/>
-    <hyperlink ref="C83" r:id="rId79h"/>
-    <hyperlink ref="C84" r:id="rId80h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
